--- a/school_2/floors/vor_spartac_2_floors.xlsx
+++ b/school_2/floors/vor_spartac_2_floors.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="858" firstSheet="1" activeTab="21"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" tabRatio="858" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="7 с" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <sheet name="Вор2э" sheetId="24" r:id="rId21"/>
     <sheet name="общий" sheetId="25" r:id="rId22"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D2" s="47">
         <f ca="1">C2-RANDBETWEEN(0, 10)/10</f>
-        <v>79.7</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D3" s="47">
         <f t="shared" ref="D3:D66" ca="1" si="0">C3-RANDBETWEEN(0, 10)/10</f>
-        <v>62.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="D4" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>84.7</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D5" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>244.8</v>
+        <v>244.4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D6" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>17.7</v>
+        <v>18.099999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="D7" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D8" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D9" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>3.7</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D10" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D11" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>102.8</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D12" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>89.399999999999991</v>
+        <v>89.1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D13" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>234.7</v>
+        <v>235.1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D14" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>62.2</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D15" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>62.6</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D16" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>18.900000000000002</v>
+        <v>19.100000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D17" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D18" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.7000000000000011</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D19" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>5.0999999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D21" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="D23" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>74.5</v>
+        <v>75.400000000000006</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D24" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>188.29999999999998</v>
+        <v>187.9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D25" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.1999999999999993</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D26" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>7.5</v>
+        <v>7.3999999999999995</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D27" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D28" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>89.3</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="D29" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>62.7</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D30" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5000000000000004</v>
+        <v>3.9000000000000004</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D32" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>63.900000000000006</v>
+        <v>63.800000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="D33" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>63.499999999999993</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="D34" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.1999999999999993</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="D35" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="D36" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>62.9</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D37" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>61.7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D38" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>116.10000000000001</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D39" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>197.4</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D40" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>19.899999999999999</v>
+        <v>20.099999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D41" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>119.8</v>
+        <v>119.7</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="D42" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>164.8</v>
+        <v>165.20000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="D43" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D44" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>21.400000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="D45" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>3.9000000000000004</v>
+        <v>3.5000000000000004</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="D46" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>5.0999999999999996</v>
+        <v>5.1999999999999993</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D47" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>8.7999999999999989</v>
+        <v>8.2999999999999989</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="D48" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.4</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="D49" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>93.4</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D50" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="D51" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>155.6</v>
+        <v>155.70000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D52" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>197.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="D53" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D55" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>89.4</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D56" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D58" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D59" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>38.299999999999997</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="D61" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D62" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>11.600000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="D63" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>72.3</v>
+        <v>72.599999999999994</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="D64" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D65" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D66" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>101.7</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="D67" s="47">
         <f t="shared" ref="D67" ca="1" si="1">C67-RANDBETWEEN(0, 10)/10</f>
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
